--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1387</v>
+        <v>1411</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:29</t>
+          <t>2026-08-19 14:32:29</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:43</t>
+          <t>2026-08-19 14:32:40</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6127</v>
+        <v>6202</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:51</t>
+          <t>2026-08-19 14:32:52</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2106</v>
+        <v>2121</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:03</t>
+          <t>2026-08-19 14:33:02</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1453</v>
+        <v>1467</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:12</t>
+          <t>2026-08-19 14:33:16</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:22</t>
+          <t>2026-08-19 14:33:27</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1399</v>
+        <v>1424</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:30</t>
+          <t>2026-08-19 14:33:40</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:38</t>
+          <t>2026-08-19 14:33:51</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:49</t>
+          <t>2026-08-19 14:34:01</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:02</t>
+          <t>2026-08-19 14:34:09</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:11</t>
+          <t>2026-08-19 14:34:19</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>21</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:25</t>
+          <t>2026-08-19 14:34:31</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:39</t>
+          <t>2026-08-19 14:34:42</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>8</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:47</t>
+          <t>2026-08-19 14:34:53</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:57</t>
+          <t>2026-08-19 14:35:04</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:07</t>
+          <t>2026-08-19 14:35:18</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:19</t>
+          <t>2026-08-19 14:35:25</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:30</t>
+          <t>2026-08-19 14:35:31</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:44</t>
+          <t>2026-08-19 14:35:38</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1746</v>
+        <v>1818</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>21</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:56</t>
+          <t>2026-08-19 14:35:48</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1480</v>
+        <v>1489</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:10</t>
+          <t>2026-08-19 14:35:54</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1418</v>
+        <v>1430</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:21</t>
+          <t>2026-08-19 14:36:02</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1418</v>
+        <v>1430</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:26</t>
+          <t>2026-08-19 14:36:10</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:34</t>
+          <t>2026-08-19 14:36:19</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1852</v>
+        <v>1871</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>22</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:48</t>
+          <t>2026-08-19 14:36:31</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:02</t>
+          <t>2026-08-19 14:36:37</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1878</v>
+        <v>1902</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:12</t>
+          <t>2026-08-19 14:36:47</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>20</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:20</t>
+          <t>2026-08-19 14:36:57</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:28</t>
+          <t>2026-08-19 14:37:04</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2962</v>
+        <v>3017</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:33</t>
+          <t>2026-08-19 14:37:15</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:47</t>
+          <t>2026-08-19 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:00</t>
+          <t>2026-08-19 14:37:35</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1001</v>
+        <v>1016</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:13</t>
+          <t>2026-08-19 14:37:45</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:21</t>
+          <t>2026-08-19 14:37:58</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:34</t>
+          <t>2026-08-19 14:38:05</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1457</v>
+        <v>1473</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:47</t>
+          <t>2026-08-19 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1580</v>
+        <v>1600</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:01</t>
+          <t>2026-08-19 14:38:30</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:16</t>
+          <t>2026-08-19 14:38:43</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3758</v>
+        <v>3789</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:25</t>
+          <t>2026-08-19 14:38:49</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3116</v>
+        <v>3174</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:38</t>
+          <t>2026-08-19 14:39:01</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:45</t>
+          <t>2026-08-19 14:39:15</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:53</t>
+          <t>2026-08-19 14:39:30</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:07</t>
+          <t>2026-08-19 14:39:38</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:18</t>
+          <t>2026-08-19 14:39:48</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2268</v>
+        <v>2299</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:25</t>
+          <t>2026-08-19 14:40:03</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2259</v>
+        <v>2286</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:38</t>
+          <t>2026-08-19 14:40:15</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1205</v>
+        <v>1233</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:52</t>
+          <t>2026-08-19 14:40:24</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:57</t>
+          <t>2026-08-19 14:40:31</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:04</t>
+          <t>2026-08-19 14:40:39</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1046</v>
+        <v>1077</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:17</t>
+          <t>2026-08-19 14:40:46</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2837</v>
+        <v>2888</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:26</t>
+          <t>2026-08-19 14:41:01</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4394</v>
+        <v>4433</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:33</t>
+          <t>2026-08-19 14:41:10</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:45</t>
+          <t>2026-08-19 14:41:24</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:55</t>
+          <t>2026-08-19 14:41:31</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:01</t>
+          <t>2026-08-19 14:41:44</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1933</v>
+        <v>1954</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:09</t>
+          <t>2026-08-19 14:41:51</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:20</t>
+          <t>2026-08-19 14:41:56</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1023</v>
+        <v>1047</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:30</t>
+          <t>2026-08-19 14:42:03</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2226</v>
+        <v>2250</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:40</t>
+          <t>2026-08-19 14:42:18</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1547</v>
+        <v>1564</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:46</t>
+          <t>2026-08-19 14:42:32</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1170</v>
+        <v>1188</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:58</t>
+          <t>2026-08-19 14:42:42</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:08</t>
+          <t>2026-08-19 14:42:55</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7256</v>
+        <v>7309</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:20</t>
+          <t>2026-08-19 14:43:02</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1262</v>
+        <v>1293</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:26</t>
+          <t>2026-08-19 14:43:11</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2190</v>
+        <v>2217</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:41</t>
+          <t>2026-08-19 14:43:21</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:54</t>
+          <t>2026-08-19 14:43:31</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:06</t>
+          <t>2026-08-19 14:43:37</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:17</t>
+          <t>2026-08-19 14:43:49</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4058</v>
+        <v>4116</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:26</t>
+          <t>2026-08-19 14:44:03</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>9</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:40</t>
+          <t>2026-08-19 14:44:14</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1415</v>
+        <v>1422</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:55</t>
+          <t>2026-08-19 14:44:29</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:05</t>
+          <t>2026-08-19 14:44:41</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1320</v>
+        <v>1342</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:18</t>
+          <t>2026-08-19 14:44:55</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:24</t>
+          <t>2026-08-19 14:45:06</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4483</v>
+        <v>4505</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>26</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:34</t>
+          <t>2026-08-19 14:45:19</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:45</t>
+          <t>2026-08-19 14:45:28</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:00</t>
+          <t>2026-08-19 14:45:34</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>637</v>
+        <v>661</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:07</t>
+          <t>2026-08-19 14:45:47</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:17</t>
+          <t>2026-08-19 14:46:01</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3540</v>
+        <v>3583</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:29</t>
+          <t>2026-08-19 14:46:09</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:34</t>
+          <t>2026-08-19 14:46:19</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:46</t>
+          <t>2026-08-19 14:46:27</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:55</t>
+          <t>2026-08-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:07</t>
+          <t>2026-08-19 14:46:45</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:21</t>
+          <t>2026-08-19 14:46:58</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:31</t>
+          <t>2026-08-19 14:47:12</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3106</v>
+        <v>3141</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:14</t>
+          <t>2026-08-19 14:47:53</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:29</t>
+          <t>2026-08-19 14:48:01</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2411</v>
+        <v>2431</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:42</t>
+          <t>2026-08-19 14:48:13</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:54</t>
+          <t>2026-08-19 14:48:26</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1411</v>
+        <v>1387</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19 14:32:29</t>
+          <t>2026-08-04 23:15:29</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-19 14:32:40</t>
+          <t>2026-08-04 23:15:43</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6202</v>
+        <v>6127</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-19 14:32:52</t>
+          <t>2026-08-04 23:15:51</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2121</v>
+        <v>2106</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-19 14:33:02</t>
+          <t>2026-08-04 23:16:03</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1467</v>
+        <v>1453</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:33:16</t>
+          <t>2026-08-04 23:16:12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-19 14:33:27</t>
+          <t>2026-08-04 23:16:22</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1424</v>
+        <v>1399</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-19 14:33:40</t>
+          <t>2026-08-04 23:16:30</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-19 14:33:51</t>
+          <t>2026-08-04 23:16:38</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>855</v>
+        <v>844</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-19 14:34:01</t>
+          <t>2026-08-04 23:16:49</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-19 14:34:09</t>
+          <t>2026-08-04 23:17:02</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-19 14:34:19</t>
+          <t>2026-08-04 23:17:11</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1906</v>
+        <v>1896</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>21</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-19 14:34:31</t>
+          <t>2026-08-04 23:17:25</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-19 14:34:42</t>
+          <t>2026-08-04 23:17:39</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>8</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-19 14:34:53</t>
+          <t>2026-08-04 23:17:47</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-19 14:35:04</t>
+          <t>2026-08-04 23:17:57</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-19 14:35:18</t>
+          <t>2026-08-04 23:18:07</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-19 14:35:25</t>
+          <t>2026-08-04 23:18:19</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-19 14:35:31</t>
+          <t>2026-08-04 23:18:30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-19 14:35:38</t>
+          <t>2026-08-04 23:18:44</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1818</v>
+        <v>1746</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>21</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-19 14:35:48</t>
+          <t>2026-08-04 23:18:56</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1489</v>
+        <v>1480</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-19 14:35:54</t>
+          <t>2026-08-04 23:19:10</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1430</v>
+        <v>1418</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-19 14:36:02</t>
+          <t>2026-08-04 23:19:21</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1430</v>
+        <v>1418</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-19 14:36:10</t>
+          <t>2026-08-04 23:19:26</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-19 14:36:19</t>
+          <t>2026-08-04 23:19:34</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1871</v>
+        <v>1852</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>22</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-19 14:36:31</t>
+          <t>2026-08-04 23:19:48</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-19 14:36:37</t>
+          <t>2026-08-04 23:20:02</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1902</v>
+        <v>1878</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-19 14:36:47</t>
+          <t>2026-08-04 23:20:12</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>20</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-19 14:36:57</t>
+          <t>2026-08-04 23:20:20</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-19 14:37:04</t>
+          <t>2026-08-04 23:20:28</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3017</v>
+        <v>2962</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-19 14:37:15</t>
+          <t>2026-08-04 23:20:33</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-19 14:37:29</t>
+          <t>2026-08-04 23:20:47</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-19 14:37:35</t>
+          <t>2026-08-04 23:21:00</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-19 14:37:45</t>
+          <t>2026-08-04 23:21:13</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-19 14:37:58</t>
+          <t>2026-08-04 23:21:21</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-19 14:38:05</t>
+          <t>2026-08-04 23:21:34</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1473</v>
+        <v>1457</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-19 14:38:17</t>
+          <t>2026-08-04 23:21:47</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1600</v>
+        <v>1580</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-19 14:38:30</t>
+          <t>2026-08-04 23:22:01</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-19 14:38:43</t>
+          <t>2026-08-04 23:22:16</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3789</v>
+        <v>3758</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-19 14:38:49</t>
+          <t>2026-08-04 23:22:25</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3174</v>
+        <v>3116</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-19 14:39:01</t>
+          <t>2026-08-04 23:22:38</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-19 14:39:15</t>
+          <t>2026-08-04 23:22:45</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-19 14:39:30</t>
+          <t>2026-08-04 23:22:53</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-19 14:39:38</t>
+          <t>2026-08-04 23:23:07</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-19 14:39:48</t>
+          <t>2026-08-04 23:23:18</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2299</v>
+        <v>2268</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-19 14:40:03</t>
+          <t>2026-08-04 23:23:25</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2286</v>
+        <v>2259</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-19 14:40:15</t>
+          <t>2026-08-04 23:23:38</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1233</v>
+        <v>1205</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-19 14:40:24</t>
+          <t>2026-08-04 23:23:52</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-19 14:40:31</t>
+          <t>2026-08-04 23:23:57</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-19 14:40:39</t>
+          <t>2026-08-04 23:24:04</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1077</v>
+        <v>1046</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-19 14:40:46</t>
+          <t>2026-08-04 23:24:17</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2888</v>
+        <v>2837</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-19 14:41:01</t>
+          <t>2026-08-04 23:24:26</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4433</v>
+        <v>4394</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-19 14:41:10</t>
+          <t>2026-08-04 23:24:33</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-19 14:41:24</t>
+          <t>2026-08-04 23:24:45</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-19 14:41:31</t>
+          <t>2026-08-04 23:24:55</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-19 14:41:44</t>
+          <t>2026-08-04 23:25:01</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1954</v>
+        <v>1933</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-19 14:41:51</t>
+          <t>2026-08-04 23:25:09</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-19 14:41:56</t>
+          <t>2026-08-04 23:25:20</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1047</v>
+        <v>1023</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-19 14:42:03</t>
+          <t>2026-08-04 23:25:30</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2250</v>
+        <v>2226</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-19 14:42:18</t>
+          <t>2026-08-04 23:25:40</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1564</v>
+        <v>1547</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-19 14:42:32</t>
+          <t>2026-08-04 23:25:46</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1188</v>
+        <v>1170</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-19 14:42:42</t>
+          <t>2026-08-04 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-19 14:42:55</t>
+          <t>2026-08-04 23:26:08</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7309</v>
+        <v>7256</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-19 14:43:02</t>
+          <t>2026-08-04 23:26:20</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1293</v>
+        <v>1262</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-19 14:43:11</t>
+          <t>2026-08-04 23:26:26</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2217</v>
+        <v>2190</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-19 14:43:21</t>
+          <t>2026-08-04 23:26:41</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-19 14:43:31</t>
+          <t>2026-08-04 23:26:54</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-19 14:43:37</t>
+          <t>2026-08-04 23:27:06</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-19 14:43:49</t>
+          <t>2026-08-04 23:27:17</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4116</v>
+        <v>4058</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-19 14:44:03</t>
+          <t>2026-08-04 23:27:26</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>9</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-19 14:44:14</t>
+          <t>2026-08-04 23:27:40</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-19 14:44:29</t>
+          <t>2026-08-04 23:27:55</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-19 14:44:41</t>
+          <t>2026-08-04 23:28:05</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1342</v>
+        <v>1320</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-19 14:44:55</t>
+          <t>2026-08-04 23:28:18</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-19 14:45:06</t>
+          <t>2026-08-04 23:28:24</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4505</v>
+        <v>4483</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>26</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-19 14:45:19</t>
+          <t>2026-08-04 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-19 14:45:28</t>
+          <t>2026-08-04 23:28:45</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-19 14:45:34</t>
+          <t>2026-08-04 23:29:00</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-19 14:45:47</t>
+          <t>2026-08-04 23:29:07</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1405</v>
+        <v>1395</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-19 14:46:01</t>
+          <t>2026-08-04 23:29:17</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3583</v>
+        <v>3540</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-19 14:46:09</t>
+          <t>2026-08-04 23:29:29</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-19 14:46:19</t>
+          <t>2026-08-04 23:29:34</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-19 14:46:27</t>
+          <t>2026-08-04 23:29:46</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-19 14:46:37</t>
+          <t>2026-08-04 23:29:55</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-19 14:46:45</t>
+          <t>2026-08-04 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>732</v>
+        <v>712</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-19 14:46:58</t>
+          <t>2026-08-04 23:30:21</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-19 14:47:12</t>
+          <t>2026-08-04 23:30:31</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3141</v>
+        <v>3106</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-19 14:47:53</t>
+          <t>2026-08-04 23:31:14</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-19 14:48:01</t>
+          <t>2026-08-04 23:31:29</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2431</v>
+        <v>2411</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-19 14:48:13</t>
+          <t>2026-08-04 23:31:42</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-19 14:48:26</t>
+          <t>2026-08-04 23:31:54</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1387</v>
+        <v>1429</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:29</t>
+          <t>2026-08-31 19:50:19</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>695</v>
+        <v>725</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:43</t>
+          <t>2026-08-31 19:50:33</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6127</v>
+        <v>6257</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:51</t>
+          <t>2026-08-31 19:50:39</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2106</v>
+        <v>2135</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:03</t>
+          <t>2026-08-31 19:50:47</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1453</v>
+        <v>1477</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:12</t>
+          <t>2026-08-31 19:50:59</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:22</t>
+          <t>2026-08-31 19:51:12</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1399</v>
+        <v>1448</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:30</t>
+          <t>2026-08-31 19:51:18</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:38</t>
+          <t>2026-08-31 19:51:29</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:49</t>
+          <t>2026-08-31 19:51:43</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:02</t>
+          <t>2026-08-31 19:51:57</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:11</t>
+          <t>2026-08-31 19:52:04</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1896</v>
+        <v>1917</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:25</t>
+          <t>2026-08-31 19:52:11</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:39</t>
+          <t>2026-08-31 19:52:25</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:47</t>
+          <t>2026-08-31 19:52:32</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:57</t>
+          <t>2026-08-31 19:52:40</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:07</t>
+          <t>2026-08-31 19:52:50</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:19</t>
+          <t>2026-08-31 19:53:00</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:30</t>
+          <t>2026-08-31 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:44</t>
+          <t>2026-08-31 19:53:26</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1746</v>
+        <v>1849</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:56</t>
+          <t>2026-08-31 19:53:37</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1480</v>
+        <v>1497</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:10</t>
+          <t>2026-08-31 19:53:50</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:21</t>
+          <t>2026-08-31 19:54:03</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:26</t>
+          <t>2026-08-31 19:54:11</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:34</t>
+          <t>2026-08-31 19:54:20</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1852</v>
+        <v>1882</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:48</t>
+          <t>2026-08-31 19:54:27</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:02</t>
+          <t>2026-08-31 19:54:39</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1878</v>
+        <v>1927</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:12</t>
+          <t>2026-08-31 19:54:47</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1301</v>
+        <v>1319</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>20</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:20</t>
+          <t>2026-08-31 19:55:00</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:28</t>
+          <t>2026-08-31 19:55:12</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2962</v>
+        <v>3039</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:33</t>
+          <t>2026-08-31 19:55:24</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:47</t>
+          <t>2026-08-31 19:55:35</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:00</t>
+          <t>2026-08-31 19:55:48</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1001</v>
+        <v>1024</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:13</t>
+          <t>2026-08-31 19:56:02</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1541</v>
+        <v>1554</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:21</t>
+          <t>2026-08-31 19:56:14</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:34</t>
+          <t>2026-08-31 19:56:24</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1457</v>
+        <v>1484</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:47</t>
+          <t>2026-08-31 19:56:30</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1580</v>
+        <v>1624</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:01</t>
+          <t>2026-08-31 19:56:42</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:16</t>
+          <t>2026-08-31 19:56:51</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3758</v>
+        <v>3819</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:25</t>
+          <t>2026-08-31 19:56:58</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3116</v>
+        <v>3216</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:38</t>
+          <t>2026-08-31 19:57:08</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>693</v>
+        <v>712</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:45</t>
+          <t>2026-08-31 19:57:19</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:53</t>
+          <t>2026-08-31 19:57:30</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:07</t>
+          <t>2026-08-31 19:57:41</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:18</t>
+          <t>2026-08-31 19:57:52</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2268</v>
+        <v>2327</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:25</t>
+          <t>2026-08-31 19:58:01</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2259</v>
+        <v>2303</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:38</t>
+          <t>2026-08-31 19:58:10</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1205</v>
+        <v>1240</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:52</t>
+          <t>2026-08-31 19:58:20</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:57</t>
+          <t>2026-08-31 19:58:28</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>7</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:04</t>
+          <t>2026-08-31 19:58:34</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1046</v>
+        <v>1090</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:17</t>
+          <t>2026-08-31 19:58:47</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2837</v>
+        <v>2918</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:26</t>
+          <t>2026-08-31 19:58:55</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4394</v>
+        <v>4469</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:33</t>
+          <t>2026-08-31 19:59:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:45</t>
+          <t>2026-08-31 19:59:14</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:55</t>
+          <t>2026-08-31 19:59:23</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:01</t>
+          <t>2026-08-31 19:59:33</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1933</v>
+        <v>1972</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:09</t>
+          <t>2026-08-31 19:59:46</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:20</t>
+          <t>2026-08-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1023</v>
+        <v>1057</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:30</t>
+          <t>2026-08-31 20:00:11</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2226</v>
+        <v>2282</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:40</t>
+          <t>2026-08-31 20:00:16</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1547</v>
+        <v>1571</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:46</t>
+          <t>2026-08-31 20:00:31</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1170</v>
+        <v>1199</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:58</t>
+          <t>2026-08-31 20:00:41</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:08</t>
+          <t>2026-08-31 20:00:53</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7256</v>
+        <v>7372</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:20</t>
+          <t>2026-08-31 20:01:05</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:26</t>
+          <t>2026-08-31 20:01:19</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2190</v>
+        <v>2227</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:41</t>
+          <t>2026-08-31 20:01:29</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:54</t>
+          <t>2026-08-31 20:01:40</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:06</t>
+          <t>2026-08-31 20:01:46</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:17</t>
+          <t>2026-08-31 20:01:58</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4058</v>
+        <v>4147</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:26</t>
+          <t>2026-08-31 20:02:04</t>
         </is>
       </c>
     </row>
@@ -3821,14 +3821,14 @@
         <v>316</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:40</t>
+          <t>2026-08-31 20:02:11</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1415</v>
+        <v>1433</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:55</t>
+          <t>2026-08-31 20:02:22</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:05</t>
+          <t>2026-08-31 20:02:28</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1320</v>
+        <v>1357</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:18</t>
+          <t>2026-08-31 20:02:39</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1587</v>
+        <v>1599</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:24</t>
+          <t>2026-08-31 20:02:49</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4483</v>
+        <v>4533</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:34</t>
+          <t>2026-08-31 20:02:54</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:45</t>
+          <t>2026-08-31 20:03:04</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:00</t>
+          <t>2026-08-31 20:03:09</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>637</v>
+        <v>670</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:07</t>
+          <t>2026-08-31 20:03:16</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1395</v>
+        <v>1413</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:17</t>
+          <t>2026-08-31 20:03:25</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3540</v>
+        <v>3618</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:29</t>
+          <t>2026-08-31 20:03:32</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>727</v>
+        <v>752</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:34</t>
+          <t>2026-08-31 20:03:44</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:46</t>
+          <t>2026-08-31 20:03:54</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>971</v>
+        <v>984</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:55</t>
+          <t>2026-08-31 20:04:00</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:07</t>
+          <t>2026-08-31 20:04:09</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:21</t>
+          <t>2026-08-31 20:04:21</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:31</t>
+          <t>2026-08-31 20:04:29</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3106</v>
+        <v>3177</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:14</t>
+          <t>2026-08-31 20:05:11</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:29</t>
+          <t>2026-08-31 20:05:26</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2411</v>
+        <v>2445</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:42</t>
+          <t>2026-08-31 20:05:38</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1372</v>
+        <v>1390</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:54</t>
+          <t>2026-08-31 20:05:45</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1429</v>
+        <v>1387</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:50:19</t>
+          <t>2026-08-04 23:15:29</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-31 19:50:33</t>
+          <t>2026-08-04 23:15:43</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6257</v>
+        <v>6127</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-31 19:50:39</t>
+          <t>2026-08-04 23:15:51</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2135</v>
+        <v>2106</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:50:47</t>
+          <t>2026-08-04 23:16:03</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1477</v>
+        <v>1453</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:50:59</t>
+          <t>2026-08-04 23:16:12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-31 19:51:12</t>
+          <t>2026-08-04 23:16:22</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1448</v>
+        <v>1399</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:51:18</t>
+          <t>2026-08-04 23:16:30</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-31 19:51:29</t>
+          <t>2026-08-04 23:16:38</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-31 19:51:43</t>
+          <t>2026-08-04 23:16:49</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-31 19:51:57</t>
+          <t>2026-08-04 23:17:02</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-31 19:52:04</t>
+          <t>2026-08-04 23:17:11</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1917</v>
+        <v>1896</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-31 19:52:11</t>
+          <t>2026-08-04 23:17:25</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-31 19:52:25</t>
+          <t>2026-08-04 23:17:39</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-31 19:52:32</t>
+          <t>2026-08-04 23:17:47</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>792</v>
+        <v>767</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-31 19:52:40</t>
+          <t>2026-08-04 23:17:57</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-31 19:52:50</t>
+          <t>2026-08-04 23:18:07</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-31 19:53:00</t>
+          <t>2026-08-04 23:18:19</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-31 19:53:12</t>
+          <t>2026-08-04 23:18:30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-31 19:53:26</t>
+          <t>2026-08-04 23:18:44</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1849</v>
+        <v>1746</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-31 19:53:37</t>
+          <t>2026-08-04 23:18:56</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1497</v>
+        <v>1480</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-31 19:53:50</t>
+          <t>2026-08-04 23:19:10</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1437</v>
+        <v>1418</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-31 19:54:03</t>
+          <t>2026-08-04 23:19:21</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1437</v>
+        <v>1418</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-31 19:54:11</t>
+          <t>2026-08-04 23:19:26</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-31 19:54:20</t>
+          <t>2026-08-04 23:19:34</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1882</v>
+        <v>1852</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-31 19:54:27</t>
+          <t>2026-08-04 23:19:48</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-31 19:54:39</t>
+          <t>2026-08-04 23:20:02</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1927</v>
+        <v>1878</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-31 19:54:47</t>
+          <t>2026-08-04 23:20:12</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1319</v>
+        <v>1301</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>20</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-31 19:55:00</t>
+          <t>2026-08-04 23:20:20</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-31 19:55:12</t>
+          <t>2026-08-04 23:20:28</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3039</v>
+        <v>2962</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-31 19:55:24</t>
+          <t>2026-08-04 23:20:33</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-31 19:55:35</t>
+          <t>2026-08-04 23:20:47</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-31 19:55:48</t>
+          <t>2026-08-04 23:21:00</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1024</v>
+        <v>1001</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-31 19:56:02</t>
+          <t>2026-08-04 23:21:13</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1554</v>
+        <v>1541</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-31 19:56:14</t>
+          <t>2026-08-04 23:21:21</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-31 19:56:24</t>
+          <t>2026-08-04 23:21:34</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1484</v>
+        <v>1457</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-31 19:56:30</t>
+          <t>2026-08-04 23:21:47</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1624</v>
+        <v>1580</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-31 19:56:42</t>
+          <t>2026-08-04 23:22:01</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-31 19:56:51</t>
+          <t>2026-08-04 23:22:16</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3819</v>
+        <v>3758</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-31 19:56:58</t>
+          <t>2026-08-04 23:22:25</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3216</v>
+        <v>3116</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-31 19:57:08</t>
+          <t>2026-08-04 23:22:38</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-31 19:57:19</t>
+          <t>2026-08-04 23:22:45</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-31 19:57:30</t>
+          <t>2026-08-04 23:22:53</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-31 19:57:41</t>
+          <t>2026-08-04 23:23:07</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-31 19:57:52</t>
+          <t>2026-08-04 23:23:18</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2327</v>
+        <v>2268</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-31 19:58:01</t>
+          <t>2026-08-04 23:23:25</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2303</v>
+        <v>2259</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-31 19:58:10</t>
+          <t>2026-08-04 23:23:38</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1240</v>
+        <v>1205</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-31 19:58:20</t>
+          <t>2026-08-04 23:23:52</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-31 19:58:28</t>
+          <t>2026-08-04 23:23:57</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>7</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-31 19:58:34</t>
+          <t>2026-08-04 23:24:04</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1090</v>
+        <v>1046</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-31 19:58:47</t>
+          <t>2026-08-04 23:24:17</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2918</v>
+        <v>2837</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-31 19:58:55</t>
+          <t>2026-08-04 23:24:26</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4469</v>
+        <v>4394</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:00</t>
+          <t>2026-08-04 23:24:33</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:14</t>
+          <t>2026-08-04 23:24:45</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:23</t>
+          <t>2026-08-04 23:24:55</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:33</t>
+          <t>2026-08-04 23:25:01</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1972</v>
+        <v>1933</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:46</t>
+          <t>2026-08-04 23:25:09</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:00</t>
+          <t>2026-08-04 23:25:20</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1057</v>
+        <v>1023</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:11</t>
+          <t>2026-08-04 23:25:30</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2282</v>
+        <v>2226</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:16</t>
+          <t>2026-08-04 23:25:40</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1571</v>
+        <v>1547</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:31</t>
+          <t>2026-08-04 23:25:46</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1199</v>
+        <v>1170</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:41</t>
+          <t>2026-08-04 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:53</t>
+          <t>2026-08-04 23:26:08</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7372</v>
+        <v>7256</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-31 20:01:05</t>
+          <t>2026-08-04 23:26:20</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1305</v>
+        <v>1262</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-31 20:01:19</t>
+          <t>2026-08-04 23:26:26</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2227</v>
+        <v>2190</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-31 20:01:29</t>
+          <t>2026-08-04 23:26:41</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-31 20:01:40</t>
+          <t>2026-08-04 23:26:54</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-31 20:01:46</t>
+          <t>2026-08-04 23:27:06</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-31 20:01:58</t>
+          <t>2026-08-04 23:27:17</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4147</v>
+        <v>4058</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-31 20:02:04</t>
+          <t>2026-08-04 23:27:26</t>
         </is>
       </c>
     </row>
@@ -3821,14 +3821,14 @@
         <v>316</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-31 20:02:11</t>
+          <t>2026-08-04 23:27:40</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-31 20:02:22</t>
+          <t>2026-08-04 23:27:55</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-31 20:02:28</t>
+          <t>2026-08-04 23:28:05</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1357</v>
+        <v>1320</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-31 20:02:39</t>
+          <t>2026-08-04 23:28:18</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1599</v>
+        <v>1587</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-31 20:02:49</t>
+          <t>2026-08-04 23:28:24</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4533</v>
+        <v>4483</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-31 20:02:54</t>
+          <t>2026-08-04 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-31 20:03:04</t>
+          <t>2026-08-04 23:28:45</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-31 20:03:09</t>
+          <t>2026-08-04 23:29:00</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>670</v>
+        <v>637</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-31 20:03:16</t>
+          <t>2026-08-04 23:29:07</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1413</v>
+        <v>1395</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-31 20:03:25</t>
+          <t>2026-08-04 23:29:17</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3618</v>
+        <v>3540</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-31 20:03:32</t>
+          <t>2026-08-04 23:29:29</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>752</v>
+        <v>727</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-31 20:03:44</t>
+          <t>2026-08-04 23:29:34</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-31 20:03:54</t>
+          <t>2026-08-04 23:29:46</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>984</v>
+        <v>971</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-31 20:04:00</t>
+          <t>2026-08-04 23:29:55</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-31 20:04:09</t>
+          <t>2026-08-04 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>740</v>
+        <v>712</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-31 20:04:21</t>
+          <t>2026-08-04 23:30:21</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-31 20:04:29</t>
+          <t>2026-08-04 23:30:31</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3177</v>
+        <v>3106</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-31 20:05:11</t>
+          <t>2026-08-04 23:31:14</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-31 20:05:26</t>
+          <t>2026-08-04 23:31:29</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2445</v>
+        <v>2411</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-31 20:05:38</t>
+          <t>2026-08-04 23:31:42</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1390</v>
+        <v>1372</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-31 20:05:45</t>
+          <t>2026-08-04 23:31:54</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1387</v>
+        <v>1433</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:29</t>
+          <t>2026-09-04 17:22:46</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:43</t>
+          <t>2026-09-04 17:22:56</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6127</v>
+        <v>6263</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:51</t>
+          <t>2026-09-04 17:23:03</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2106</v>
+        <v>2136</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:03</t>
+          <t>2026-09-04 17:23:15</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1453</v>
+        <v>1481</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:12</t>
+          <t>2026-09-04 17:23:21</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:22</t>
+          <t>2026-09-04 17:23:30</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1399</v>
+        <v>1450</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:30</t>
+          <t>2026-09-04 17:23:43</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:38</t>
+          <t>2026-09-04 17:23:55</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:49</t>
+          <t>2026-09-04 17:24:06</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:02</t>
+          <t>2026-09-04 17:24:15</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:11</t>
+          <t>2026-09-04 17:24:23</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1896</v>
+        <v>1917</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:25</t>
+          <t>2026-09-04 17:24:33</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:39</t>
+          <t>2026-09-04 17:24:42</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:47</t>
+          <t>2026-09-04 17:24:56</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:57</t>
+          <t>2026-09-04 17:25:11</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:07</t>
+          <t>2026-09-04 17:25:19</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:19</t>
+          <t>2026-09-04 17:25:34</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:30</t>
+          <t>2026-09-04 17:25:41</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:44</t>
+          <t>2026-09-04 17:25:47</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1746</v>
+        <v>1854</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:56</t>
+          <t>2026-09-04 17:26:02</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1480</v>
+        <v>1501</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:10</t>
+          <t>2026-09-04 17:26:09</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:21</t>
+          <t>2026-09-04 17:26:20</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:26</t>
+          <t>2026-09-04 17:26:29</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1667,17 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>676</v>
+        <v>702</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:34</t>
+          <t>2026-09-04 17:26:40</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1852</v>
+        <v>1883</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:48</t>
+          <t>2026-09-04 17:26:49</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:02</t>
+          <t>2026-09-04 17:26:59</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1878</v>
+        <v>1931</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:12</t>
+          <t>2026-09-04 17:27:06</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1301</v>
+        <v>1331</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:20</t>
+          <t>2026-09-04 17:27:17</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:28</t>
+          <t>2026-09-04 17:27:29</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2962</v>
+        <v>3045</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:33</t>
+          <t>2026-09-04 17:27:39</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:47</t>
+          <t>2026-09-04 17:27:48</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:00</t>
+          <t>2026-09-04 17:27:56</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1001</v>
+        <v>1025</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:13</t>
+          <t>2026-09-04 17:28:10</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1541</v>
+        <v>1554</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:21</t>
+          <t>2026-09-04 17:28:22</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:34</t>
+          <t>2026-09-04 17:28:37</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1457</v>
+        <v>1486</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:47</t>
+          <t>2026-09-04 17:28:44</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1580</v>
+        <v>1629</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:01</t>
+          <t>2026-09-04 17:28:56</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:16</t>
+          <t>2026-09-04 17:29:07</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3758</v>
+        <v>3826</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:25</t>
+          <t>2026-09-04 17:29:16</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3116</v>
+        <v>3223</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:38</t>
+          <t>2026-09-04 17:29:21</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:45</t>
+          <t>2026-09-04 17:29:29</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:53</t>
+          <t>2026-09-04 17:29:42</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:07</t>
+          <t>2026-09-04 17:29:51</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:18</t>
+          <t>2026-09-04 17:30:05</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2268</v>
+        <v>2333</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:25</t>
+          <t>2026-09-04 17:30:17</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2259</v>
+        <v>2308</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:38</t>
+          <t>2026-09-04 17:30:29</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1205</v>
+        <v>1240</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:52</t>
+          <t>2026-09-04 17:30:37</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:57</t>
+          <t>2026-09-04 17:30:52</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>7</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:04</t>
+          <t>2026-09-04 17:31:00</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1046</v>
+        <v>1091</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:17</t>
+          <t>2026-09-04 17:31:14</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2837</v>
+        <v>2927</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:26</t>
+          <t>2026-09-04 17:31:26</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4394</v>
+        <v>4473</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:33</t>
+          <t>2026-09-04 17:31:41</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:45</t>
+          <t>2026-09-04 17:31:55</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:55</t>
+          <t>2026-09-04 17:32:02</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:01</t>
+          <t>2026-09-04 17:32:14</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1933</v>
+        <v>1973</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:09</t>
+          <t>2026-09-04 17:32:23</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:20</t>
+          <t>2026-09-04 17:32:31</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1023</v>
+        <v>1060</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:30</t>
+          <t>2026-09-04 17:32:36</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2226</v>
+        <v>2285</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:40</t>
+          <t>2026-09-04 17:32:49</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1547</v>
+        <v>1575</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:46</t>
+          <t>2026-09-04 17:32:56</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1170</v>
+        <v>1204</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:58</t>
+          <t>2026-09-04 17:33:05</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:08</t>
+          <t>2026-09-04 17:33:12</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7256</v>
+        <v>7384</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:20</t>
+          <t>2026-09-04 17:33:19</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:26</t>
+          <t>2026-09-04 17:33:32</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2190</v>
+        <v>2235</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:41</t>
+          <t>2026-09-04 17:33:43</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:54</t>
+          <t>2026-09-04 17:33:51</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:06</t>
+          <t>2026-09-04 17:34:00</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:17</t>
+          <t>2026-09-04 17:34:10</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4058</v>
+        <v>4149</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:26</t>
+          <t>2026-09-04 17:34:18</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:40</t>
+          <t>2026-09-04 17:34:29</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1415</v>
+        <v>1433</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:55</t>
+          <t>2026-09-04 17:34:43</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:05</t>
+          <t>2026-09-04 17:34:57</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1320</v>
+        <v>1358</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:18</t>
+          <t>2026-09-04 17:35:11</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1587</v>
+        <v>1601</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:24</t>
+          <t>2026-09-04 17:35:20</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4483</v>
+        <v>4541</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:34</t>
+          <t>2026-09-04 17:35:30</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:45</t>
+          <t>2026-09-04 17:35:40</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:00</t>
+          <t>2026-09-04 17:35:54</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>637</v>
+        <v>673</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:07</t>
+          <t>2026-09-04 17:35:59</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1395</v>
+        <v>1415</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:17</t>
+          <t>2026-09-04 17:36:11</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3540</v>
+        <v>3624</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:29</t>
+          <t>2026-09-04 17:36:21</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>727</v>
+        <v>753</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:34</t>
+          <t>2026-09-04 17:36:31</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:46</t>
+          <t>2026-09-04 17:36:38</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>971</v>
+        <v>987</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:55</t>
+          <t>2026-09-04 17:36:52</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>781</v>
+        <v>805</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:07</t>
+          <t>2026-09-04 17:37:00</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:21</t>
+          <t>2026-09-04 17:37:13</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:31</t>
+          <t>2026-09-04 17:37:26</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3106</v>
+        <v>3188</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:14</t>
+          <t>2026-09-04 17:38:07</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:29</t>
+          <t>2026-09-04 17:38:22</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2411</v>
+        <v>2449</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:42</t>
+          <t>2026-09-04 17:38:29</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1372</v>
+        <v>1390</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:54</t>
+          <t>2026-09-04 17:38:38</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1433</v>
+        <v>1387</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 17:22:46</t>
+          <t>2026-08-04 23:15:29</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>726</v>
+        <v>695</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-04 17:22:56</t>
+          <t>2026-08-04 23:15:43</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6263</v>
+        <v>6127</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-04 17:23:03</t>
+          <t>2026-08-04 23:15:51</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2136</v>
+        <v>2106</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-04 17:23:15</t>
+          <t>2026-08-04 23:16:03</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1481</v>
+        <v>1453</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-04 17:23:21</t>
+          <t>2026-08-04 23:16:12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-04 17:23:30</t>
+          <t>2026-08-04 23:16:22</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1450</v>
+        <v>1399</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-04 17:23:43</t>
+          <t>2026-08-04 23:16:30</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-04 17:23:55</t>
+          <t>2026-08-04 23:16:38</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>865</v>
+        <v>844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-04 17:24:06</t>
+          <t>2026-08-04 23:16:49</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-04 17:24:15</t>
+          <t>2026-08-04 23:17:02</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-04 17:24:23</t>
+          <t>2026-08-04 23:17:11</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1917</v>
+        <v>1896</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-04 17:24:33</t>
+          <t>2026-08-04 23:17:25</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-04 17:24:42</t>
+          <t>2026-08-04 23:17:39</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-04 17:24:56</t>
+          <t>2026-08-04 23:17:47</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>792</v>
+        <v>767</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-04 17:25:11</t>
+          <t>2026-08-04 23:17:57</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-04 17:25:19</t>
+          <t>2026-08-04 23:18:07</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-04 17:25:34</t>
+          <t>2026-08-04 23:18:19</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-04 17:25:41</t>
+          <t>2026-08-04 23:18:30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-04 17:25:47</t>
+          <t>2026-08-04 23:18:44</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1854</v>
+        <v>1746</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-04 17:26:02</t>
+          <t>2026-08-04 23:18:56</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1501</v>
+        <v>1480</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-04 17:26:09</t>
+          <t>2026-08-04 23:19:10</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1437</v>
+        <v>1418</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-04 17:26:20</t>
+          <t>2026-08-04 23:19:21</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1437</v>
+        <v>1418</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-04 17:26:29</t>
+          <t>2026-08-04 23:19:26</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1667,17 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>702</v>
+        <v>676</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-04 17:26:40</t>
+          <t>2026-08-04 23:19:34</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1883</v>
+        <v>1852</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-04 17:26:49</t>
+          <t>2026-08-04 23:19:48</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-04 17:26:59</t>
+          <t>2026-08-04 23:20:02</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1931</v>
+        <v>1878</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-04 17:27:06</t>
+          <t>2026-08-04 23:20:12</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1331</v>
+        <v>1301</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-04 17:27:17</t>
+          <t>2026-08-04 23:20:20</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>625</v>
+        <v>606</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-04 17:27:29</t>
+          <t>2026-08-04 23:20:28</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3045</v>
+        <v>2962</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-04 17:27:39</t>
+          <t>2026-08-04 23:20:33</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-04 17:27:48</t>
+          <t>2026-08-04 23:20:47</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-04 17:27:56</t>
+          <t>2026-08-04 23:21:00</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1025</v>
+        <v>1001</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-04 17:28:10</t>
+          <t>2026-08-04 23:21:13</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1554</v>
+        <v>1541</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-04 17:28:22</t>
+          <t>2026-08-04 23:21:21</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-04 17:28:37</t>
+          <t>2026-08-04 23:21:34</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1486</v>
+        <v>1457</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-04 17:28:44</t>
+          <t>2026-08-04 23:21:47</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1629</v>
+        <v>1580</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-04 17:28:56</t>
+          <t>2026-08-04 23:22:01</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-04 17:29:07</t>
+          <t>2026-08-04 23:22:16</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3826</v>
+        <v>3758</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-04 17:29:16</t>
+          <t>2026-08-04 23:22:25</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3223</v>
+        <v>3116</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-04 17:29:21</t>
+          <t>2026-08-04 23:22:38</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>713</v>
+        <v>693</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-04 17:29:29</t>
+          <t>2026-08-04 23:22:45</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-04 17:29:42</t>
+          <t>2026-08-04 23:22:53</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-04 17:29:51</t>
+          <t>2026-08-04 23:23:07</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-04 17:30:05</t>
+          <t>2026-08-04 23:23:18</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2333</v>
+        <v>2268</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-04 17:30:17</t>
+          <t>2026-08-04 23:23:25</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2308</v>
+        <v>2259</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-04 17:30:29</t>
+          <t>2026-08-04 23:23:38</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1240</v>
+        <v>1205</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-04 17:30:37</t>
+          <t>2026-08-04 23:23:52</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-04 17:30:52</t>
+          <t>2026-08-04 23:23:57</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>7</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-04 17:31:00</t>
+          <t>2026-08-04 23:24:04</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1091</v>
+        <v>1046</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-04 17:31:14</t>
+          <t>2026-08-04 23:24:17</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2927</v>
+        <v>2837</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-04 17:31:26</t>
+          <t>2026-08-04 23:24:26</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4473</v>
+        <v>4394</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-04 17:31:41</t>
+          <t>2026-08-04 23:24:33</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-04 17:31:55</t>
+          <t>2026-08-04 23:24:45</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-04 17:32:02</t>
+          <t>2026-08-04 23:24:55</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-04 17:32:14</t>
+          <t>2026-08-04 23:25:01</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1973</v>
+        <v>1933</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-04 17:32:23</t>
+          <t>2026-08-04 23:25:09</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-04 17:32:31</t>
+          <t>2026-08-04 23:25:20</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1060</v>
+        <v>1023</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-04 17:32:36</t>
+          <t>2026-08-04 23:25:30</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2285</v>
+        <v>2226</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-04 17:32:49</t>
+          <t>2026-08-04 23:25:40</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1575</v>
+        <v>1547</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-04 17:32:56</t>
+          <t>2026-08-04 23:25:46</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1204</v>
+        <v>1170</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-04 17:33:05</t>
+          <t>2026-08-04 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-04 17:33:12</t>
+          <t>2026-08-04 23:26:08</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7384</v>
+        <v>7256</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-04 17:33:19</t>
+          <t>2026-08-04 23:26:20</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1305</v>
+        <v>1262</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-04 17:33:32</t>
+          <t>2026-08-04 23:26:26</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2235</v>
+        <v>2190</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-04 17:33:43</t>
+          <t>2026-08-04 23:26:41</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-04 17:33:51</t>
+          <t>2026-08-04 23:26:54</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-04 17:34:00</t>
+          <t>2026-08-04 23:27:06</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-04 17:34:10</t>
+          <t>2026-08-04 23:27:17</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4149</v>
+        <v>4058</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-04 17:34:18</t>
+          <t>2026-08-04 23:27:26</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-04 17:34:29</t>
+          <t>2026-08-04 23:27:40</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-04 17:34:43</t>
+          <t>2026-08-04 23:27:55</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-04 17:34:57</t>
+          <t>2026-08-04 23:28:05</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1358</v>
+        <v>1320</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-09-04 17:35:11</t>
+          <t>2026-08-04 23:28:18</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1601</v>
+        <v>1587</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-09-04 17:35:20</t>
+          <t>2026-08-04 23:28:24</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4541</v>
+        <v>4483</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-09-04 17:35:30</t>
+          <t>2026-08-04 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-04 17:35:40</t>
+          <t>2026-08-04 23:28:45</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-09-04 17:35:54</t>
+          <t>2026-08-04 23:29:00</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>673</v>
+        <v>637</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-09-04 17:35:59</t>
+          <t>2026-08-04 23:29:07</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1415</v>
+        <v>1395</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-09-04 17:36:11</t>
+          <t>2026-08-04 23:29:17</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3624</v>
+        <v>3540</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-04 17:36:21</t>
+          <t>2026-08-04 23:29:29</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>753</v>
+        <v>727</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-04 17:36:31</t>
+          <t>2026-08-04 23:29:34</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-04 17:36:38</t>
+          <t>2026-08-04 23:29:46</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-04 17:36:52</t>
+          <t>2026-08-04 23:29:55</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>805</v>
+        <v>781</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-04 17:37:00</t>
+          <t>2026-08-04 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>740</v>
+        <v>712</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-04 17:37:13</t>
+          <t>2026-08-04 23:30:21</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-04 17:37:26</t>
+          <t>2026-08-04 23:30:31</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3188</v>
+        <v>3106</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-04 17:38:07</t>
+          <t>2026-08-04 23:31:14</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-04 17:38:22</t>
+          <t>2026-08-04 23:31:29</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2449</v>
+        <v>2411</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-04 17:38:29</t>
+          <t>2026-08-04 23:31:42</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1390</v>
+        <v>1372</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-04 17:38:38</t>
+          <t>2026-08-04 23:31:54</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1387</v>
+        <v>1435</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:29</t>
+          <t>2026-09-06 16:42:39</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>695</v>
+        <v>728</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:43</t>
+          <t>2026-09-06 16:42:47</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6127</v>
+        <v>6267</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:51</t>
+          <t>2026-09-06 16:42:57</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2106</v>
+        <v>2138</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:03</t>
+          <t>2026-09-06 16:43:05</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1453</v>
+        <v>1483</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:12</t>
+          <t>2026-09-06 16:43:16</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:22</t>
+          <t>2026-09-06 16:43:22</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1399</v>
+        <v>1453</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:30</t>
+          <t>2026-09-06 16:43:35</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:38</t>
+          <t>2026-09-06 16:43:44</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:49</t>
+          <t>2026-09-06 16:43:59</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:02</t>
+          <t>2026-09-06 16:44:04</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:11</t>
+          <t>2026-09-06 16:44:18</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1896</v>
+        <v>1918</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:25</t>
+          <t>2026-09-06 16:44:26</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:39</t>
+          <t>2026-09-06 16:44:33</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:47</t>
+          <t>2026-09-06 16:44:44</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:57</t>
+          <t>2026-09-06 16:44:59</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:07</t>
+          <t>2026-09-06 16:45:11</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:19</t>
+          <t>2026-09-06 16:45:19</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:30</t>
+          <t>2026-09-06 16:45:31</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:44</t>
+          <t>2026-09-06 16:45:36</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1746</v>
+        <v>1855</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:56</t>
+          <t>2026-09-06 16:45:51</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1480</v>
+        <v>1502</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:10</t>
+          <t>2026-09-06 16:46:00</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:21</t>
+          <t>2026-09-06 16:46:09</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:26</t>
+          <t>2026-09-06 16:46:22</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1667,17 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>676</v>
+        <v>702</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:34</t>
+          <t>2026-09-06 16:46:28</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1852</v>
+        <v>1883</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:48</t>
+          <t>2026-09-06 16:46:37</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:02</t>
+          <t>2026-09-06 16:46:44</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1878</v>
+        <v>1933</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:12</t>
+          <t>2026-09-06 16:46:59</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1301</v>
+        <v>1331</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:20</t>
+          <t>2026-09-06 16:47:04</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>606</v>
+        <v>628</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:28</t>
+          <t>2026-09-06 16:47:16</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2962</v>
+        <v>3045</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:33</t>
+          <t>2026-09-06 16:47:26</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:47</t>
+          <t>2026-09-06 16:47:36</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:00</t>
+          <t>2026-09-06 16:47:42</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:13</t>
+          <t>2026-09-06 16:47:56</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:21</t>
+          <t>2026-09-06 16:48:12</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:34</t>
+          <t>2026-09-06 16:48:17</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1457</v>
+        <v>1486</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:47</t>
+          <t>2026-09-06 16:48:30</t>
         </is>
       </c>
     </row>
@@ -2265,17 +2265,17 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1580</v>
+        <v>1631</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:01</t>
+          <t>2026-09-06 16:48:44</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:16</t>
+          <t>2026-09-06 16:48:54</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3758</v>
+        <v>3830</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:25</t>
+          <t>2026-09-06 16:49:01</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3116</v>
+        <v>3232</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:38</t>
+          <t>2026-09-06 16:49:13</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:45</t>
+          <t>2026-09-06 16:49:21</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:53</t>
+          <t>2026-09-06 16:49:35</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:07</t>
+          <t>2026-09-06 16:49:42</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:18</t>
+          <t>2026-09-06 16:49:53</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2268</v>
+        <v>2335</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:25</t>
+          <t>2026-09-06 16:50:07</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2259</v>
+        <v>2310</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:38</t>
+          <t>2026-09-06 16:50:14</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1205</v>
+        <v>1244</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:52</t>
+          <t>2026-09-06 16:50:22</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:57</t>
+          <t>2026-09-06 16:50:33</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>7</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:04</t>
+          <t>2026-09-06 16:50:45</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1046</v>
+        <v>1091</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:17</t>
+          <t>2026-09-06 16:50:57</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2837</v>
+        <v>2930</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:26</t>
+          <t>2026-09-06 16:51:08</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4394</v>
+        <v>4477</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:33</t>
+          <t>2026-09-06 16:51:18</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:45</t>
+          <t>2026-09-06 16:51:27</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:55</t>
+          <t>2026-09-06 16:51:41</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:01</t>
+          <t>2026-09-06 16:51:48</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1933</v>
+        <v>1974</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:09</t>
+          <t>2026-09-06 16:51:55</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:20</t>
+          <t>2026-09-06 16:52:09</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1023</v>
+        <v>1061</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:30</t>
+          <t>2026-09-06 16:52:22</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2226</v>
+        <v>2287</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:40</t>
+          <t>2026-09-06 16:52:29</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1547</v>
+        <v>1577</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:46</t>
+          <t>2026-09-06 16:52:40</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1170</v>
+        <v>1204</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:58</t>
+          <t>2026-09-06 16:52:48</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:08</t>
+          <t>2026-09-06 16:52:54</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7256</v>
+        <v>7388</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:20</t>
+          <t>2026-09-06 16:53:03</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1262</v>
+        <v>1307</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:26</t>
+          <t>2026-09-06 16:53:09</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2190</v>
+        <v>2237</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:41</t>
+          <t>2026-09-06 16:53:17</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:54</t>
+          <t>2026-09-06 16:53:31</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:06</t>
+          <t>2026-09-06 16:53:44</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:17</t>
+          <t>2026-09-06 16:53:56</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4058</v>
+        <v>4149</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:26</t>
+          <t>2026-09-06 16:54:03</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:40</t>
+          <t>2026-09-06 16:54:14</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1415</v>
+        <v>1433</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:55</t>
+          <t>2026-09-06 16:54:23</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:05</t>
+          <t>2026-09-06 16:54:32</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1320</v>
+        <v>1360</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:18</t>
+          <t>2026-09-06 16:54:43</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1587</v>
+        <v>1604</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:24</t>
+          <t>2026-09-06 16:54:56</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4483</v>
+        <v>4545</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:34</t>
+          <t>2026-09-06 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:45</t>
+          <t>2026-09-06 16:55:22</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:00</t>
+          <t>2026-09-06 16:55:31</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>637</v>
+        <v>673</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:07</t>
+          <t>2026-09-06 16:55:37</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1395</v>
+        <v>1414</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:17</t>
+          <t>2026-09-06 16:55:46</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3540</v>
+        <v>3625</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:29</t>
+          <t>2026-09-06 16:55:56</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>727</v>
+        <v>755</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:34</t>
+          <t>2026-09-06 16:56:06</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:46</t>
+          <t>2026-09-06 16:56:15</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:55</t>
+          <t>2026-09-06 16:56:24</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>781</v>
+        <v>807</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:07</t>
+          <t>2026-09-06 16:56:35</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:21</t>
+          <t>2026-09-06 16:56:43</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>548</v>
+        <v>570</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:31</t>
+          <t>2026-09-06 16:56:54</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3106</v>
+        <v>3189</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:14</t>
+          <t>2026-09-06 16:57:39</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:29</t>
+          <t>2026-09-06 16:57:49</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2411</v>
+        <v>2449</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:42</t>
+          <t>2026-09-06 16:57:56</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:54</t>
+          <t>2026-09-06 16:58:06</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1435</v>
+        <v>1387</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06 16:42:39</t>
+          <t>2026-08-04 23:15:29</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-06 16:42:47</t>
+          <t>2026-08-04 23:15:43</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6267</v>
+        <v>6127</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-06 16:42:57</t>
+          <t>2026-08-04 23:15:51</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2138</v>
+        <v>2106</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-06 16:43:05</t>
+          <t>2026-08-04 23:16:03</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1483</v>
+        <v>1453</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-06 16:43:16</t>
+          <t>2026-08-04 23:16:12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-06 16:43:22</t>
+          <t>2026-08-04 23:16:22</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1453</v>
+        <v>1399</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-06 16:43:35</t>
+          <t>2026-08-04 23:16:30</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-06 16:43:44</t>
+          <t>2026-08-04 23:16:38</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>865</v>
+        <v>844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-06 16:43:59</t>
+          <t>2026-08-04 23:16:49</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-06 16:44:04</t>
+          <t>2026-08-04 23:17:02</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-06 16:44:18</t>
+          <t>2026-08-04 23:17:11</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1918</v>
+        <v>1896</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-06 16:44:26</t>
+          <t>2026-08-04 23:17:25</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-06 16:44:33</t>
+          <t>2026-08-04 23:17:39</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-06 16:44:44</t>
+          <t>2026-08-04 23:17:47</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>792</v>
+        <v>767</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-06 16:44:59</t>
+          <t>2026-08-04 23:17:57</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-06 16:45:11</t>
+          <t>2026-08-04 23:18:07</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-06 16:45:19</t>
+          <t>2026-08-04 23:18:19</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-06 16:45:31</t>
+          <t>2026-08-04 23:18:30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-06 16:45:36</t>
+          <t>2026-08-04 23:18:44</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1855</v>
+        <v>1746</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-06 16:45:51</t>
+          <t>2026-08-04 23:18:56</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1502</v>
+        <v>1480</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:00</t>
+          <t>2026-08-04 23:19:10</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1437</v>
+        <v>1418</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:09</t>
+          <t>2026-08-04 23:19:21</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1437</v>
+        <v>1418</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:22</t>
+          <t>2026-08-04 23:19:26</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1667,17 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>702</v>
+        <v>676</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:28</t>
+          <t>2026-08-04 23:19:34</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1883</v>
+        <v>1852</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:37</t>
+          <t>2026-08-04 23:19:48</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:44</t>
+          <t>2026-08-04 23:20:02</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1933</v>
+        <v>1878</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:59</t>
+          <t>2026-08-04 23:20:12</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1331</v>
+        <v>1301</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-06 16:47:04</t>
+          <t>2026-08-04 23:20:20</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-06 16:47:16</t>
+          <t>2026-08-04 23:20:28</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3045</v>
+        <v>2962</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-06 16:47:26</t>
+          <t>2026-08-04 23:20:33</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-06 16:47:36</t>
+          <t>2026-08-04 23:20:47</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-06 16:47:42</t>
+          <t>2026-08-04 23:21:00</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1026</v>
+        <v>1001</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-06 16:47:56</t>
+          <t>2026-08-04 23:21:13</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1555</v>
+        <v>1541</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-06 16:48:12</t>
+          <t>2026-08-04 23:21:21</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-06 16:48:17</t>
+          <t>2026-08-04 23:21:34</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1486</v>
+        <v>1457</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-06 16:48:30</t>
+          <t>2026-08-04 23:21:47</t>
         </is>
       </c>
     </row>
@@ -2265,17 +2265,17 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1631</v>
+        <v>1580</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-06 16:48:44</t>
+          <t>2026-08-04 23:22:01</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-06 16:48:54</t>
+          <t>2026-08-04 23:22:16</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3830</v>
+        <v>3758</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:01</t>
+          <t>2026-08-04 23:22:25</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3232</v>
+        <v>3116</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:13</t>
+          <t>2026-08-04 23:22:38</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:21</t>
+          <t>2026-08-04 23:22:45</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:35</t>
+          <t>2026-08-04 23:22:53</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:42</t>
+          <t>2026-08-04 23:23:07</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:53</t>
+          <t>2026-08-04 23:23:18</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2335</v>
+        <v>2268</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:07</t>
+          <t>2026-08-04 23:23:25</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2310</v>
+        <v>2259</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:14</t>
+          <t>2026-08-04 23:23:38</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:22</t>
+          <t>2026-08-04 23:23:52</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:33</t>
+          <t>2026-08-04 23:23:57</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>7</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:45</t>
+          <t>2026-08-04 23:24:04</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1091</v>
+        <v>1046</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:57</t>
+          <t>2026-08-04 23:24:17</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2930</v>
+        <v>2837</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-06 16:51:08</t>
+          <t>2026-08-04 23:24:26</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4477</v>
+        <v>4394</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-06 16:51:18</t>
+          <t>2026-08-04 23:24:33</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-06 16:51:27</t>
+          <t>2026-08-04 23:24:45</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-06 16:51:41</t>
+          <t>2026-08-04 23:24:55</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-06 16:51:48</t>
+          <t>2026-08-04 23:25:01</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1974</v>
+        <v>1933</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-06 16:51:55</t>
+          <t>2026-08-04 23:25:09</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-06 16:52:09</t>
+          <t>2026-08-04 23:25:20</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1061</v>
+        <v>1023</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-06 16:52:22</t>
+          <t>2026-08-04 23:25:30</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2287</v>
+        <v>2226</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-06 16:52:29</t>
+          <t>2026-08-04 23:25:40</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1577</v>
+        <v>1547</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-06 16:52:40</t>
+          <t>2026-08-04 23:25:46</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1204</v>
+        <v>1170</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-06 16:52:48</t>
+          <t>2026-08-04 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-06 16:52:54</t>
+          <t>2026-08-04 23:26:08</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7388</v>
+        <v>7256</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>47</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-06 16:53:03</t>
+          <t>2026-08-04 23:26:20</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1307</v>
+        <v>1262</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-06 16:53:09</t>
+          <t>2026-08-04 23:26:26</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2237</v>
+        <v>2190</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-06 16:53:17</t>
+          <t>2026-08-04 23:26:41</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-06 16:53:31</t>
+          <t>2026-08-04 23:26:54</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-06 16:53:44</t>
+          <t>2026-08-04 23:27:06</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-06 16:53:56</t>
+          <t>2026-08-04 23:27:17</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4149</v>
+        <v>4058</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:03</t>
+          <t>2026-08-04 23:27:26</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:14</t>
+          <t>2026-08-04 23:27:40</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:23</t>
+          <t>2026-08-04 23:27:55</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:32</t>
+          <t>2026-08-04 23:28:05</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1360</v>
+        <v>1320</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:43</t>
+          <t>2026-08-04 23:28:18</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1604</v>
+        <v>1587</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:56</t>
+          <t>2026-08-04 23:28:24</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4545</v>
+        <v>4483</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-09-06 16:55:08</t>
+          <t>2026-08-04 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-06 16:55:22</t>
+          <t>2026-08-04 23:28:45</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-09-06 16:55:31</t>
+          <t>2026-08-04 23:29:00</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>673</v>
+        <v>637</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-09-06 16:55:37</t>
+          <t>2026-08-04 23:29:07</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1414</v>
+        <v>1395</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-09-06 16:55:46</t>
+          <t>2026-08-04 23:29:17</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3625</v>
+        <v>3540</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>32</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-06 16:55:56</t>
+          <t>2026-08-04 23:29:29</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>755</v>
+        <v>727</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-06 16:56:06</t>
+          <t>2026-08-04 23:29:34</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-06 16:56:15</t>
+          <t>2026-08-04 23:29:46</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>986</v>
+        <v>971</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-06 16:56:24</t>
+          <t>2026-08-04 23:29:55</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>807</v>
+        <v>781</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-06 16:56:35</t>
+          <t>2026-08-04 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>740</v>
+        <v>712</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-06 16:56:43</t>
+          <t>2026-08-04 23:30:21</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-06 16:56:54</t>
+          <t>2026-08-04 23:30:31</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3189</v>
+        <v>3106</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-06 16:57:39</t>
+          <t>2026-08-04 23:31:14</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-06 16:57:49</t>
+          <t>2026-08-04 23:31:29</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2449</v>
+        <v>2411</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-06 16:57:56</t>
+          <t>2026-08-04 23:31:42</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1391</v>
+        <v>1372</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-06 16:58:06</t>
+          <t>2026-08-04 23:31:54</t>
         </is>
       </c>
     </row>
